--- a/docs/ledger-templates/运转一车间现员分布台账.xlsx
+++ b/docs/ledger-templates/运转一车间现员分布台账.xlsx
@@ -32,15 +32,7 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="281">
   <si>
     <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">        新港编组场车间     </t>
+      <t xml:space="preserve">        运转一车间     </t>
     </r>
     <r>
       <rPr>
@@ -904,7 +896,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -924,13 +916,6 @@
       <color theme="1"/>
       <name val="黑体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1419,30 +1404,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top style="thin">
         <color auto="1"/>
@@ -1457,6 +1418,30 @@
       <right style="thin">
         <color auto="1"/>
       </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -1583,137 +1568,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1732,7 +1717,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="57" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="57" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="57" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1741,100 +1726,112 @@
     <xf numFmtId="57" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2277,15 +2274,15 @@
       <c r="K3" s="12"/>
       <c r="L3" s="12"/>
       <c r="M3" s="12"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="35"/>
-      <c r="R3" s="35"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
       <c r="S3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T3" s="36" t="s">
+      <c r="T3" s="40" t="s">
         <v>7</v>
       </c>
       <c r="U3" s="9" t="s">
@@ -2296,521 +2293,531 @@
       <c r="A4" s="13"/>
       <c r="B4" s="14"/>
       <c r="C4" s="13"/>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11" t="s">
+      <c r="E4" s="16"/>
+      <c r="F4" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11" t="s">
+      <c r="G4" s="16"/>
+      <c r="H4" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11" t="s">
+      <c r="I4" s="16"/>
+      <c r="J4" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11" t="s">
+      <c r="K4" s="16"/>
+      <c r="L4" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="11"/>
-      <c r="N4" s="36" t="s">
+      <c r="M4" s="16"/>
+      <c r="N4" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="O4" s="36" t="s">
+      <c r="O4" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="36" t="s">
+      <c r="P4" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="Q4" s="36" t="s">
+      <c r="Q4" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="R4" s="36" t="s">
+      <c r="R4" s="40" t="s">
         <v>18</v>
       </c>
       <c r="S4" s="13"/>
-      <c r="T4" s="36"/>
+      <c r="T4" s="40"/>
       <c r="U4" s="13"/>
     </row>
     <row r="5" ht="25.25" customHeight="1" spans="1:21">
-      <c r="A5" s="15"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="11" t="s">
+      <c r="A5" s="17"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11" t="s">
+      <c r="E5" s="20"/>
+      <c r="F5" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11" t="s">
+      <c r="G5" s="20"/>
+      <c r="H5" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11" t="s">
+      <c r="I5" s="20"/>
+      <c r="J5" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11" t="s">
+      <c r="K5" s="20"/>
+      <c r="L5" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="M5" s="11"/>
-      <c r="N5" s="36" t="s">
+      <c r="M5" s="20"/>
+      <c r="N5" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="O5" s="36" t="s">
+      <c r="O5" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="P5" s="36" t="s">
+      <c r="P5" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="Q5" s="36" t="s">
+      <c r="Q5" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="R5" s="36" t="s">
+      <c r="R5" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="S5" s="15"/>
+      <c r="S5" s="17"/>
       <c r="T5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="U5" s="15"/>
+      <c r="U5" s="17"/>
     </row>
     <row r="6" ht="24.4" customHeight="1" spans="1:21">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
-      <c r="O6" s="21"/>
-      <c r="P6" s="21"/>
-      <c r="Q6" s="21"/>
-      <c r="R6" s="21"/>
-      <c r="S6" s="17"/>
-      <c r="T6" s="17"/>
-      <c r="U6" s="17"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="21"/>
+      <c r="T6" s="21"/>
+      <c r="U6" s="21"/>
     </row>
     <row r="7" ht="24.4" customHeight="1" spans="1:21">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="17"/>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="17"/>
-      <c r="R7" s="17"/>
-      <c r="S7" s="17"/>
-      <c r="T7" s="17"/>
-      <c r="U7" s="17"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="21"/>
+      <c r="T7" s="21"/>
+      <c r="U7" s="21"/>
     </row>
     <row r="8" ht="24.4" customHeight="1" spans="1:21">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="21"/>
-      <c r="N8" s="21"/>
-      <c r="O8" s="21"/>
-      <c r="P8" s="21"/>
-      <c r="Q8" s="21"/>
-      <c r="R8" s="21"/>
-      <c r="S8" s="17"/>
-      <c r="T8" s="17"/>
-      <c r="U8" s="17"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="21"/>
+      <c r="T8" s="21"/>
+      <c r="U8" s="21"/>
     </row>
     <row r="9" ht="24.4" customHeight="1" spans="1:21">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="17"/>
-      <c r="R9" s="17"/>
-      <c r="S9" s="17"/>
-      <c r="T9" s="17"/>
-      <c r="U9" s="17"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="21"/>
+      <c r="S9" s="21"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="21"/>
     </row>
     <row r="10" ht="24.4" customHeight="1" spans="1:21">
-      <c r="A10" s="24"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="25"/>
-      <c r="O10" s="25"/>
-      <c r="P10" s="25"/>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="25"/>
-      <c r="S10" s="24"/>
-      <c r="T10" s="24"/>
-      <c r="U10" s="24"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="29"/>
+      <c r="R10" s="29"/>
+      <c r="S10" s="28"/>
+      <c r="T10" s="28"/>
+      <c r="U10" s="28"/>
     </row>
     <row r="11" ht="24.4" customHeight="1" spans="1:21">
-      <c r="A11" s="24"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="24"/>
-      <c r="N11" s="24"/>
-      <c r="O11" s="24"/>
-      <c r="P11" s="24"/>
-      <c r="Q11" s="24"/>
-      <c r="R11" s="24"/>
-      <c r="S11" s="24"/>
-      <c r="T11" s="24"/>
-      <c r="U11" s="24"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="28"/>
+      <c r="Q11" s="28"/>
+      <c r="R11" s="28"/>
+      <c r="S11" s="28"/>
+      <c r="T11" s="28"/>
+      <c r="U11" s="28"/>
     </row>
     <row r="12" ht="24.4" customHeight="1" spans="1:21">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="24"/>
-      <c r="Q12" s="24"/>
-      <c r="R12" s="24"/>
-      <c r="S12" s="24"/>
-      <c r="T12" s="24"/>
-      <c r="U12" s="24"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+      <c r="M12" s="28"/>
+      <c r="N12" s="28"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="28"/>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="28"/>
+      <c r="S12" s="28"/>
+      <c r="T12" s="28"/>
+      <c r="U12" s="28"/>
     </row>
     <row r="13" ht="24.4" customHeight="1" spans="1:21">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="24"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="24"/>
-      <c r="R13" s="24"/>
-      <c r="S13" s="24"/>
-      <c r="T13" s="24"/>
-      <c r="U13" s="24"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="28"/>
+      <c r="O13" s="28"/>
+      <c r="P13" s="28"/>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="28"/>
+      <c r="S13" s="28"/>
+      <c r="T13" s="28"/>
+      <c r="U13" s="28"/>
     </row>
     <row r="14" ht="24.4" customHeight="1" spans="1:21">
-      <c r="A14" s="24"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="24"/>
-      <c r="U14" s="24"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="28"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="28"/>
+      <c r="Q14" s="28"/>
+      <c r="R14" s="28"/>
+      <c r="S14" s="28"/>
+      <c r="T14" s="28"/>
+      <c r="U14" s="28"/>
     </row>
     <row r="15" ht="24.4" customHeight="1" spans="1:21">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="24"/>
-      <c r="R15" s="24"/>
-      <c r="S15" s="24"/>
-      <c r="T15" s="24"/>
-      <c r="U15" s="24"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="28"/>
+      <c r="R15" s="28"/>
+      <c r="S15" s="28"/>
+      <c r="T15" s="28"/>
+      <c r="U15" s="28"/>
     </row>
     <row r="16" ht="24.4" customHeight="1" spans="1:21">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
-      <c r="R16" s="24"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="24"/>
-      <c r="U16" s="24"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28"/>
+      <c r="U16" s="28"/>
     </row>
     <row r="17" ht="24.4" customHeight="1" spans="1:21">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="24"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="24"/>
-      <c r="R17" s="24"/>
-      <c r="S17" s="24"/>
-      <c r="T17" s="24"/>
-      <c r="U17" s="24"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="28"/>
+      <c r="N17" s="28"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="28"/>
+      <c r="Q17" s="28"/>
+      <c r="R17" s="28"/>
+      <c r="S17" s="28"/>
+      <c r="T17" s="28"/>
+      <c r="U17" s="28"/>
     </row>
     <row r="18" ht="24.4" customHeight="1" spans="1:21">
-      <c r="A18" s="24"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="24"/>
-      <c r="O18" s="24"/>
-      <c r="P18" s="24"/>
-      <c r="Q18" s="24"/>
-      <c r="R18" s="24"/>
-      <c r="S18" s="24"/>
-      <c r="T18" s="24"/>
-      <c r="U18" s="24"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="28"/>
+      <c r="N18" s="28"/>
+      <c r="O18" s="28"/>
+      <c r="P18" s="28"/>
+      <c r="Q18" s="28"/>
+      <c r="R18" s="28"/>
+      <c r="S18" s="28"/>
+      <c r="T18" s="28"/>
+      <c r="U18" s="28"/>
     </row>
     <row r="19" ht="24.4" customHeight="1" spans="1:21">
-      <c r="A19" s="24"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
-      <c r="Q19" s="24"/>
-      <c r="R19" s="24"/>
-      <c r="S19" s="24"/>
-      <c r="T19" s="24"/>
-      <c r="U19" s="24"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="28"/>
+      <c r="Q19" s="28"/>
+      <c r="R19" s="28"/>
+      <c r="S19" s="28"/>
+      <c r="T19" s="28"/>
+      <c r="U19" s="28"/>
     </row>
     <row r="20" ht="24.4" customHeight="1" spans="1:21">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="28"/>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="28"/>
-      <c r="U20" s="38"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="32"/>
+      <c r="R20" s="32"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="42"/>
     </row>
     <row r="21" ht="24.4" customHeight="1" spans="1:21">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="29"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
-      <c r="L21" s="30"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="30"/>
-      <c r="O21" s="30"/>
-      <c r="P21" s="30"/>
-      <c r="Q21" s="30"/>
-      <c r="R21" s="30"/>
-      <c r="S21" s="30"/>
-      <c r="T21" s="30"/>
-      <c r="U21" s="39"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34"/>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="34"/>
+      <c r="P21" s="34"/>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34"/>
+      <c r="U21" s="43"/>
     </row>
     <row r="22" ht="24.4" customHeight="1" spans="1:21">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="31"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
-      <c r="L22" s="32"/>
-      <c r="M22" s="32"/>
-      <c r="N22" s="32"/>
-      <c r="O22" s="32"/>
-      <c r="P22" s="32"/>
-      <c r="Q22" s="32"/>
-      <c r="R22" s="32"/>
-      <c r="S22" s="32"/>
-      <c r="T22" s="32"/>
-      <c r="U22" s="40"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
+      <c r="S22" s="36"/>
+      <c r="T22" s="36"/>
+      <c r="U22" s="44"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="33"/>
-      <c r="B24" s="34"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
+      <c r="A24" s="37"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="33"/>
-      <c r="B25" s="34"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
+      <c r="A25" s="37"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="33"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37"/>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="33"/>
+      <c r="A27" s="37"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="21">
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
     <mergeCell ref="B20:U20"/>
     <mergeCell ref="B21:U21"/>
     <mergeCell ref="B22:U22"/>
